--- a/artfynd/A 56704-2022 artfynd.xlsx
+++ b/artfynd/A 56704-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 56704-2022 artfynd.xlsx
+++ b/artfynd/A 56704-2022 artfynd.xlsx
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114567205</v>
+        <v>114567207</v>
       </c>
       <c r="B2" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -723,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582676</v>
+        <v>582618</v>
       </c>
       <c r="R2" t="n">
-        <v>6655999</v>
+        <v>6655867</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,12 +748,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-06-08</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-06-08</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114954866</v>
+        <v>114567205</v>
       </c>
       <c r="B3" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -824,24 +814,20 @@
           <t>30</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Granängen,ca 700 m SV om (knärot), Vstm</t>
+          <t>Munga-Horndal, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>582676</v>
       </c>
       <c r="R3" t="n">
-        <v>6656000</v>
+        <v>6655999</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,11 +850,6 @@
       <c r="W3" t="inlineStr">
         <is>
           <t>Möklinta</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>U-Sal-0842</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -894,7 +875,7 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bo Eriksson</t>
+          <t>Mårten Nilsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -902,11 +883,7 @@
           <t>Maria Edstam</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige, Inventering längs blivande kraftledning Munga-Horndal</t>
-        </is>
-      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56704-2022 artfynd.xlsx
+++ b/artfynd/A 56704-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114567207</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,8 +894,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114567205</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>